--- a/Result/profitability/6154.xlsx
+++ b/Result/profitability/6154.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>1.04</v>
       </c>
       <c r="M2" t="n">
-        <v>0.29375</v>
+        <v>0.2975</v>
       </c>
       <c r="N2" t="n">
-        <v>16.72375</v>
+        <v>17.12</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.41</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3150000000000001</v>
+        <v>0.33875</v>
       </c>
       <c r="N3" t="n">
-        <v>16.5175</v>
+        <v>16.84375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.51</v>
       </c>
       <c r="M4" t="n">
-        <v>0.36875</v>
+        <v>0.3825</v>
       </c>
       <c r="N4" t="n">
-        <v>16.09875</v>
+        <v>16.48125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="N5" t="n">
-        <v>16.17</v>
+        <v>16.68875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.64</v>
       </c>
       <c r="M6" t="n">
-        <v>0.47625</v>
+        <v>0.5</v>
       </c>
       <c r="N6" t="n">
-        <v>15.93</v>
+        <v>16.37375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.21</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4925</v>
+        <v>0.48625</v>
       </c>
       <c r="N7" t="n">
-        <v>15.895</v>
+        <v>15.97125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4775</v>
+        <v>0.45125</v>
       </c>
       <c r="N8" t="n">
-        <v>15.23</v>
+        <v>15.2275</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.76</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5125</v>
+        <v>0.5125000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>14.96875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6154</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>962</v>
+      </c>
+      <c r="D75" t="n">
+        <v>776</v>
+      </c>
+      <c r="E75" t="n">
+        <v>186</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>28</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.86%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>27</v>
+      </c>
+      <c r="K75" t="n">
+        <v>22</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1975</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.22875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4374999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.01999999999999957</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.001031459515213995</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2726675427069645</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
